--- a/Lingvistik_proj/ausen-persuasion_head_lingvistik.xlsx
+++ b/Lingvistik_proj/ausen-persuasion_head_lingvistik.xlsx
@@ -543,7 +543,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ausen-emma_S_2341_L_1</t>
+          <t>ausen-emma_S#2341_L#1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -623,7 +623,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ausen-emma_S_2727_L_2</t>
+          <t>ausen-emma_S#2727_L#2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -703,7 +703,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ausen-emma_S_2936_L_3</t>
+          <t>ausen-emma_S#2936_L#3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ausen-emma_S_11884_L_4</t>
+          <t>ausen-emma_S#11884_L#4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -859,7 +859,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ausen-emma_S_13694_L_5</t>
+          <t>ausen-emma_S#13694_L#5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -939,7 +939,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ausen-emma_S_16168_L_6</t>
+          <t>ausen-emma_S#16168_L#6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1019,7 +1019,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ausen-emma_S_24059_L_7</t>
+          <t>ausen-emma_S#24059_L#7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ausen-emma_S_26305_L_8</t>
+          <t>ausen-emma_S#26305_L#8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1183,7 +1183,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ausen-emma_S_35885_L_9</t>
+          <t>ausen-emma_S#35885_L#9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1267,7 +1267,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ausen-emma_S_39630_L_10</t>
+          <t>ausen-emma_S#39630_L#10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ausen-emma_S_40374_L_11</t>
+          <t>ausen-emma_S#40374_L#11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1427,7 +1427,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ausen-emma_S_41464_L_12</t>
+          <t>ausen-emma_S#41464_L#12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1511,7 +1511,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ausen-emma_S_52610_L_13</t>
+          <t>ausen-emma_S#52610_L#13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1595,7 +1595,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ausen-emma_S_68950_L_14</t>
+          <t>ausen-emma_S#68950_L#14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1679,7 +1679,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ausen-emma_S_76580_L_15</t>
+          <t>ausen-emma_S#76580_L#15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1751,7 +1751,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ausen-emma_S_83449_L_16</t>
+          <t>ausen-emma_S#83449_L#16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1831,7 +1831,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ausen-emma_S_86346_L_17</t>
+          <t>ausen-emma_S#86346_L#17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1915,7 +1915,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ausen-emma_S_86843_L_18</t>
+          <t>ausen-emma_S#86843_L#18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1991,7 +1991,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ausen-emma_S_93472_L_19</t>
+          <t>ausen-emma_S#93472_L#19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ausen-emma_S_94613_L_20</t>
+          <t>ausen-emma_S#94613_L#20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2159,7 +2159,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ausen-emma_S_100395_L_21</t>
+          <t>ausen-emma_S#100395_L#21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2239,7 +2239,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ausen-emma_S_102584_L_22</t>
+          <t>ausen-emma_S#102584_L#22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2323,7 +2323,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ausen-emma_S_104031_L_23</t>
+          <t>ausen-emma_S#104031_L#23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2403,7 +2403,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ausen-emma_S_104106_L_24</t>
+          <t>ausen-emma_S#104106_L#24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2487,7 +2487,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ausen-emma_S_107310_L_25</t>
+          <t>ausen-emma_S#107310_L#25</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2567,7 +2567,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ausen-emma_S_112173_L_26</t>
+          <t>ausen-emma_S#112173_L#26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2647,7 +2647,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ausen-emma_S_116281_L_27</t>
+          <t>ausen-emma_S#116281_L#27</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2727,7 +2727,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ausen-emma_S_119658_L_28</t>
+          <t>ausen-emma_S#119658_L#28</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2811,7 +2811,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ausen-emma_S_126934_L_29</t>
+          <t>ausen-emma_S#126934_L#29</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2895,7 +2895,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ausen-emma_S_128454_L_30</t>
+          <t>ausen-emma_S#128454_L#30</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2975,7 +2975,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ausen-emma_S_129603_L_31</t>
+          <t>ausen-emma_S#129603_L#31</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3059,7 +3059,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ausen-emma_S_136556_L_32</t>
+          <t>ausen-emma_S#136556_L#32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3139,7 +3139,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ausen-emma_S_149874_L_33</t>
+          <t>ausen-emma_S#149874_L#33</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3223,7 +3223,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ausen-emma_S_150755_L_34</t>
+          <t>ausen-emma_S#150755_L#34</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3307,7 +3307,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ausen-emma_S_151760_L_35</t>
+          <t>ausen-emma_S#151760_L#35</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ausen-emma_S_156585_L_36</t>
+          <t>ausen-emma_S#156585_L#36</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3475,7 +3475,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ausen-emma_S_161276_L_37</t>
+          <t>ausen-emma_S#161276_L#37</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3551,7 +3551,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ausen-emma_S_174778_L_38</t>
+          <t>ausen-emma_S#174778_L#38</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3635,7 +3635,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ausen-emma_S_178199_L_39</t>
+          <t>ausen-emma_S#178199_L#39</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3715,7 +3715,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ausen-emma_S_186688_L_40</t>
+          <t>ausen-emma_S#186688_L#40</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3787,7 +3787,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ausen-emma_S_188417_L_41</t>
+          <t>ausen-emma_S#188417_L#41</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3867,7 +3867,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ausen-emma_S_188454_L_42</t>
+          <t>ausen-emma_S#188454_L#42</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3943,7 +3943,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_835_L_1</t>
+          <t>ausen-persuasion_S#835_L#1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4019,7 +4019,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_2124_L_2</t>
+          <t>ausen-persuasion_S#2124_L#2</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4103,7 +4103,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_3785_L_3</t>
+          <t>ausen-persuasion_S#3785_L#3</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4187,7 +4187,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_4799_L_4</t>
+          <t>ausen-persuasion_S#4799_L#4</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4271,7 +4271,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_6804_L_5</t>
+          <t>ausen-persuasion_S#6804_L#5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4351,7 +4351,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_17778_L_6</t>
+          <t>ausen-persuasion_S#17778_L#6</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4435,7 +4435,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_18393_L_7</t>
+          <t>ausen-persuasion_S#18393_L#7</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4519,7 +4519,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_18469_L_8</t>
+          <t>ausen-persuasion_S#18469_L#8</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4603,7 +4603,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_19932_L_9</t>
+          <t>ausen-persuasion_S#19932_L#9</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4687,7 +4687,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_23012_L_10</t>
+          <t>ausen-persuasion_S#23012_L#10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_28878_L_11</t>
+          <t>ausen-persuasion_S#28878_L#11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4855,7 +4855,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_29882_L_12</t>
+          <t>ausen-persuasion_S#29882_L#12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4939,7 +4939,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_30275_L_13</t>
+          <t>ausen-persuasion_S#30275_L#13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5023,7 +5023,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_34068_L_14</t>
+          <t>ausen-persuasion_S#34068_L#14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5107,7 +5107,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_37838_L_15</t>
+          <t>ausen-persuasion_S#37838_L#15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5191,7 +5191,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_38528_L_16</t>
+          <t>ausen-persuasion_S#38528_L#16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5275,7 +5275,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_42993_L_17</t>
+          <t>ausen-persuasion_S#42993_L#17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -5359,7 +5359,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_43173_L_18</t>
+          <t>ausen-persuasion_S#43173_L#18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -5435,7 +5435,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_47604_L_19</t>
+          <t>ausen-persuasion_S#47604_L#19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5515,7 +5515,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_47617_L_20</t>
+          <t>ausen-persuasion_S#47617_L#20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5591,7 +5591,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_48511_L_21</t>
+          <t>ausen-persuasion_S#48511_L#21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5675,7 +5675,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_49333_L_22</t>
+          <t>ausen-persuasion_S#49333_L#22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5755,7 +5755,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_50144_L_23</t>
+          <t>ausen-persuasion_S#50144_L#23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -5839,7 +5839,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_50290_L_24</t>
+          <t>ausen-persuasion_S#50290_L#24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -5923,7 +5923,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_55754_L_25</t>
+          <t>ausen-persuasion_S#55754_L#25</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6007,7 +6007,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_55769_L_26</t>
+          <t>ausen-persuasion_S#55769_L#26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6091,7 +6091,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_56396_L_27</t>
+          <t>ausen-persuasion_S#56396_L#27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6175,7 +6175,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_57014_L_28</t>
+          <t>ausen-persuasion_S#57014_L#28</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6247,7 +6247,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_60680_L_29</t>
+          <t>ausen-persuasion_S#60680_L#29</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6327,7 +6327,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_63041_L_30</t>
+          <t>ausen-persuasion_S#63041_L#30</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6411,7 +6411,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_68827_L_31</t>
+          <t>ausen-persuasion_S#68827_L#31</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -6495,7 +6495,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_75032_L_32</t>
+          <t>ausen-persuasion_S#75032_L#32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6575,7 +6575,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_75748_L_33</t>
+          <t>ausen-persuasion_S#75748_L#33</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6655,7 +6655,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_75757_L_34</t>
+          <t>ausen-persuasion_S#75757_L#34</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6739,7 +6739,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_88763_L_35</t>
+          <t>ausen-persuasion_S#88763_L#35</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6823,7 +6823,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_88859_L_36</t>
+          <t>ausen-persuasion_S#88859_L#36</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6899,7 +6899,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_89737_L_37</t>
+          <t>ausen-persuasion_S#89737_L#37</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6983,7 +6983,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_89894_L_38</t>
+          <t>ausen-persuasion_S#89894_L#38</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -7067,7 +7067,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_92943_L_39</t>
+          <t>ausen-persuasion_S#92943_L#39</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -7151,7 +7151,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>ausen-persuasion_S_96641_L_40</t>
+          <t>ausen-persuasion_S#96641_L#40</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
